--- a/Tagihan/2026/Agustus/Pa Itab/PA ITAB REVISI.xlsx
+++ b/Tagihan/2026/Agustus/Pa Itab/PA ITAB REVISI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\2026\Agustus\Pa Itab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E569565-18F5-4F95-94B4-CB3DB644B69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B920FA1-4321-4AC8-8E69-7D52157329EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>NO.</t>
   </si>
@@ -474,30 +474,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -554,6 +530,26 @@
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -641,6 +637,42 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -650,20 +682,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -681,35 +701,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -783,13 +779,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>59532</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2403475</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>115571</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1124,7 +1120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A5:H40"/>
+  <dimension ref="A5:H43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" customWidth="1"/>
@@ -1140,47 +1136,47 @@
     <row r="5" spans="2:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
     </row>
     <row r="8" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
     </row>
     <row r="9" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
     </row>
     <row r="10" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
     </row>
     <row r="11" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
     </row>
     <row r="12" spans="2:7" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F12" s="7"/>
@@ -1190,20 +1186,20 @@
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="43" t="s">
+      <c r="F13" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="43"/>
+      <c r="G13" s="51"/>
     </row>
     <row r="14" spans="2:7" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="44" t="s">
+      <c r="F14" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="44"/>
+      <c r="G14" s="52"/>
     </row>
     <row r="15" spans="2:7" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C15" s="23"/>
@@ -1230,10 +1226,10 @@
       </c>
     </row>
     <row r="17" spans="1:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="50" t="s">
+      <c r="B17" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="51"/>
+      <c r="C17" s="41"/>
       <c r="D17" s="25"/>
       <c r="E17" s="25"/>
       <c r="F17" s="15"/>
@@ -1280,12 +1276,8 @@
       <c r="C20" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="2">
-        <v>20</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
       <c r="F20" s="14"/>
       <c r="G20" s="16"/>
     </row>
@@ -1294,8 +1286,12 @@
       <c r="C21" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="17"/>
+      <c r="D21" s="2">
+        <v>20</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="F21" s="14"/>
       <c r="G21" s="16"/>
     </row>
@@ -1303,10 +1299,10 @@
       <c r="A22" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="52" t="s">
+      <c r="B22" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="53"/>
+      <c r="C22" s="43"/>
       <c r="D22" s="2"/>
       <c r="E22" s="17"/>
       <c r="F22" s="14"/>
@@ -1319,15 +1315,9 @@
       <c r="C23" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="2">
-        <v>2</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" s="14">
-        <v>350000</v>
-      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="14"/>
       <c r="G23" s="16"/>
     </row>
     <row r="24" spans="1:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1335,9 +1325,15 @@
       <c r="C24" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="14"/>
+      <c r="D24" s="2">
+        <v>3</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="14">
+        <v>350000</v>
+      </c>
       <c r="G24" s="16"/>
     </row>
     <row r="25" spans="1:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1365,12 +1361,8 @@
       <c r="C26" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D26" s="2">
-        <v>2</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>18</v>
-      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
       <c r="F26" s="14"/>
       <c r="G26" s="16"/>
     </row>
@@ -1379,23 +1371,27 @@
       <c r="C27" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="2"/>
+      <c r="D27" s="2">
+        <v>1</v>
+      </c>
       <c r="E27" s="19"/>
       <c r="F27" s="16"/>
       <c r="G27" s="15"/>
     </row>
     <row r="28" spans="1:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="54"/>
+      <c r="B28" s="32"/>
       <c r="C28" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="2"/>
+      <c r="D28" s="2">
+        <v>1</v>
+      </c>
       <c r="E28" s="17"/>
       <c r="F28" s="16"/>
       <c r="G28" s="16"/>
     </row>
     <row r="29" spans="1:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="54">
+      <c r="B29" s="32">
         <v>4</v>
       </c>
       <c r="C29" s="17" t="s">
@@ -1418,87 +1414,111 @@
       <c r="D30" s="2"/>
       <c r="E30" s="22"/>
       <c r="F30" s="16"/>
-      <c r="G30" s="55"/>
-    </row>
-    <row r="31" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="48" t="s">
+      <c r="G30" s="33"/>
+    </row>
+    <row r="31" spans="1:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="2"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="33"/>
+    </row>
+    <row r="32" spans="1:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="2"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="33"/>
+    </row>
+    <row r="33" spans="2:8" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="2"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="33"/>
+    </row>
+    <row r="34" spans="2:8" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="C31" s="49"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="18">
+      <c r="C34" s="55"/>
+      <c r="D34" s="55"/>
+      <c r="E34" s="55"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="18">
         <f>SUM(G17:G27)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="8"/>
-    </row>
-    <row r="34" spans="2:8" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B34" s="41" t="s">
+    <row r="35" spans="2:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="8"/>
+    </row>
+    <row r="37" spans="2:8" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B37" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="C34" s="41"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="42" t="s">
+      <c r="C37" s="49"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="G34" s="42"/>
-    </row>
-    <row r="38" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B38" s="47"/>
-      <c r="C38" s="47"/>
-      <c r="D38" s="47"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="47"/>
-      <c r="G38" s="47"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="38" t="s">
+      <c r="G37" s="50"/>
+    </row>
+    <row r="41" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B41" s="39"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="39"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B42" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="39"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="12"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="35" t="s">
+      <c r="C42" s="38"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="12"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B43" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="36"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="46"/>
-      <c r="H40" s="12"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="36"/>
+      <c r="H43" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B22:C22"/>
     <mergeCell ref="C7:G8"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C11:G11"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="B34:F34"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="F37:G37"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.23622047244094491" top="7.874015748031496E-2" bottom="0.74803149606299213" header="0.59055118110236227" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="85" orientation="portrait" horizontalDpi="4294967294" verticalDpi="300" r:id="rId1"/>
